--- a/Assets/Data/Excel/map.xlsx
+++ b/Assets/Data/Excel/map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cube\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F14C82-E7F6-491B-B875-750A61CFB2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12FF885-5824-4964-B5DD-990554EDBF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -48,9 +48,6 @@
     <t>baseLife</t>
   </si>
   <si>
-    <t>waveGroupId</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -78,12 +75,6 @@
     <t>描述</t>
   </si>
   <si>
-    <t>地图ID，对应 Assets/Data/Map/{mapId}.json</t>
-  </si>
-  <si>
-    <t>初始TD金币，金币也是Item</t>
-  </si>
-  <si>
     <t>基地初始生命</t>
   </si>
   <si>
@@ -106,13 +97,98 @@
   </si>
   <si>
     <t>使用地图2，给更多初始金币和更高基地生命</t>
+  </si>
+  <si>
+    <t>Assets/Data/Bin/Wave/wave1.bytes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Data/Bin/Wave/wave2.bytes</t>
+  </si>
+  <si>
+    <t>Assets/Data/Bin/Wave/wave3.bytes</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>waveEasy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>waveNormal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地图</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初始</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TD</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>金币</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>waveHard</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -131,6 +207,29 @@
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -160,12 +259,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -335,19 +437,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
-    <col min="5" max="5" width="60.5" customWidth="1"/>
-    <col min="6" max="6" width="39.5" customWidth="1"/>
+    <col min="5" max="6" width="18.875" customWidth="1"/>
     <col min="7" max="7" width="27.875" customWidth="1"/>
     <col min="8" max="8" width="41.875" customWidth="1"/>
+    <col min="9" max="9" width="27.125" customWidth="1"/>
+    <col min="10" max="10" width="36.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24" customHeight="1">
+    <row r="1" spans="1:10" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -370,97 +473,121 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="24" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="3" spans="1:10" ht="24" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="4" spans="1:10" ht="24" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="24" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1">
+    <row r="5" spans="1:10" ht="30" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -471,20 +598,26 @@
       <c r="G5" s="2">
         <v>20</v>
       </c>
-      <c r="H5" s="2">
-        <v>1</v>
+      <c r="H5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1">
+    <row r="6" spans="1:10" ht="30" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -495,20 +628,26 @@
       <c r="G6" s="2">
         <v>20</v>
       </c>
-      <c r="H6" s="2">
-        <v>2</v>
+      <c r="H6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1">
+    <row r="7" spans="1:10" ht="30" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2">
         <v>2</v>
@@ -519,8 +658,14 @@
       <c r="G7" s="2">
         <v>30</v>
       </c>
-      <c r="H7" s="2">
-        <v>3</v>
+      <c r="H7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Excel/map.xlsx
+++ b/Assets/Data/Excel/map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cube\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12FF885-5824-4964-B5DD-990554EDBF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967A53AF-8D79-4BE6-BC24-D70F03DD9347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9600" yWindow="0" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="td_stage" sheetId="1" r:id="rId1"/>
@@ -596,7 +596,7 @@
         <v>300</v>
       </c>
       <c r="G5" s="2">
-        <v>20</v>
+        <v>2000</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>24</v>
